--- a/data/ocean-freight.xlsx
+++ b/data/ocean-freight.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jin\Desktop\AI\자료\해상운임\9월\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jin\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4543914-DA3E-4A20-8E18-6427F5A96788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C72ECC99-6222-4E71-9857-FE7D8796BFFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25510" yWindow="0" windowWidth="25780" windowHeight="20970" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1434,10 +1434,10 @@
         <v>11</v>
       </c>
       <c r="E2" s="13">
-        <v>8500</v>
+        <v>9200</v>
       </c>
       <c r="F2" s="13">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="G2" s="16">
         <v>1</v>
@@ -1458,10 +1458,10 @@
         <v>13</v>
       </c>
       <c r="E3" s="13">
-        <v>9300</v>
+        <v>11000</v>
       </c>
       <c r="F3" s="13">
-        <v>11300</v>
+        <v>11900</v>
       </c>
       <c r="G3" s="16">
         <v>2</v>
@@ -1482,10 +1482,10 @@
         <v>15</v>
       </c>
       <c r="E4" s="13">
-        <v>9300</v>
+        <v>11000</v>
       </c>
       <c r="F4" s="13">
-        <v>11300</v>
+        <v>11900</v>
       </c>
       <c r="G4" s="16">
         <v>3</v>
@@ -1506,10 +1506,10 @@
         <v>17</v>
       </c>
       <c r="E5" s="13">
-        <v>9300</v>
+        <v>11000</v>
       </c>
       <c r="F5" s="13">
-        <v>11300</v>
+        <v>11900</v>
       </c>
       <c r="G5" s="16">
         <v>4</v>
@@ -1530,10 +1530,10 @@
         <v>19</v>
       </c>
       <c r="E6" s="13">
-        <v>6400</v>
+        <v>6700</v>
       </c>
       <c r="F6" s="13">
-        <v>7900</v>
+        <v>8500</v>
       </c>
       <c r="G6" s="16">
         <v>5</v>
@@ -1554,10 +1554,10 @@
         <v>21</v>
       </c>
       <c r="E7" s="13">
-        <v>6400</v>
+        <v>6700</v>
       </c>
       <c r="F7" s="13">
-        <v>7900</v>
+        <v>8500</v>
       </c>
       <c r="G7" s="16">
         <v>6</v>
@@ -1578,10 +1578,10 @@
         <v>23</v>
       </c>
       <c r="E8" s="13">
-        <v>6400</v>
+        <v>6700</v>
       </c>
       <c r="F8" s="13">
-        <v>7900</v>
+        <v>8500</v>
       </c>
       <c r="G8" s="16">
         <v>7</v>
@@ -1602,10 +1602,10 @@
         <v>25</v>
       </c>
       <c r="E9" s="13">
-        <v>6400</v>
+        <v>6700</v>
       </c>
       <c r="F9" s="13">
-        <v>7900</v>
+        <v>8500</v>
       </c>
       <c r="G9" s="16">
         <v>8</v>
@@ -1626,10 +1626,10 @@
         <v>27</v>
       </c>
       <c r="E10" s="13">
-        <v>8350</v>
+        <v>9200</v>
       </c>
       <c r="F10" s="13">
-        <v>9850</v>
+        <v>11000</v>
       </c>
       <c r="G10" s="16">
         <v>9</v>
@@ -1650,10 +1650,10 @@
         <v>29</v>
       </c>
       <c r="E11" s="13">
-        <v>8350</v>
+        <v>9200</v>
       </c>
       <c r="F11" s="13">
-        <v>9850</v>
+        <v>11000</v>
       </c>
       <c r="G11" s="16">
         <v>10</v>
@@ -1674,10 +1674,10 @@
         <v>31</v>
       </c>
       <c r="E12" s="13">
-        <v>8500</v>
+        <v>9200</v>
       </c>
       <c r="F12" s="13">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="G12" s="16">
         <v>11</v>
@@ -1698,10 +1698,10 @@
         <v>33</v>
       </c>
       <c r="E13" s="13">
-        <v>8500</v>
+        <v>9200</v>
       </c>
       <c r="F13" s="13">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="G13" s="16">
         <v>12</v>
@@ -1722,10 +1722,10 @@
         <v>35</v>
       </c>
       <c r="E14" s="13">
-        <v>6400</v>
+        <v>6700</v>
       </c>
       <c r="F14" s="13">
-        <v>7900</v>
+        <v>8500</v>
       </c>
       <c r="G14" s="16">
         <v>13</v>
@@ -1746,10 +1746,10 @@
         <v>38</v>
       </c>
       <c r="E15" s="13">
-        <v>8300</v>
+        <v>5200</v>
       </c>
       <c r="F15" s="13">
-        <v>8400</v>
+        <v>5600</v>
       </c>
       <c r="G15" s="16">
         <v>1</v>
@@ -1770,10 +1770,10 @@
         <v>40</v>
       </c>
       <c r="E16" s="13">
-        <v>6800</v>
+        <v>5850</v>
       </c>
       <c r="F16" s="13">
-        <v>7000</v>
+        <v>6000</v>
       </c>
       <c r="G16" s="16">
         <v>2</v>
@@ -1794,10 +1794,10 @@
         <v>42</v>
       </c>
       <c r="E17" s="13">
-        <v>6800</v>
+        <v>5850</v>
       </c>
       <c r="F17" s="13">
-        <v>7000</v>
+        <v>6000</v>
       </c>
       <c r="G17" s="16">
         <v>3</v>
@@ -1818,10 +1818,10 @@
         <v>44</v>
       </c>
       <c r="E18" s="13">
-        <v>6800</v>
+        <v>5850</v>
       </c>
       <c r="F18" s="13">
-        <v>7000</v>
+        <v>6000</v>
       </c>
       <c r="G18" s="16">
         <v>4</v>
@@ -1842,10 +1842,10 @@
         <v>46</v>
       </c>
       <c r="E19" s="13">
-        <v>8300</v>
+        <v>5200</v>
       </c>
       <c r="F19" s="13">
-        <v>8400</v>
+        <v>5600</v>
       </c>
       <c r="G19" s="16">
         <v>5</v>
@@ -1866,10 +1866,10 @@
         <v>48</v>
       </c>
       <c r="E20" s="13">
-        <v>8300</v>
+        <v>5200</v>
       </c>
       <c r="F20" s="13">
-        <v>8400</v>
+        <v>5600</v>
       </c>
       <c r="G20" s="16">
         <v>6</v>
@@ -1890,10 +1890,10 @@
         <v>50</v>
       </c>
       <c r="E21" s="13">
-        <v>9000</v>
+        <v>6200</v>
       </c>
       <c r="F21" s="13">
-        <v>9300</v>
+        <v>6300</v>
       </c>
       <c r="G21" s="16">
         <v>7</v>
@@ -1914,10 +1914,10 @@
         <v>52</v>
       </c>
       <c r="E22" s="13">
-        <v>8000</v>
+        <v>5900</v>
       </c>
       <c r="F22" s="13">
-        <v>9000</v>
+        <v>6400</v>
       </c>
       <c r="G22" s="16">
         <v>8</v>
@@ -1938,10 +1938,10 @@
         <v>55</v>
       </c>
       <c r="E23" s="13">
-        <v>3500</v>
+        <v>3100</v>
       </c>
       <c r="F23" s="13">
-        <v>5000</v>
+        <v>4100</v>
       </c>
       <c r="G23" s="16">
         <v>1</v>
@@ -1962,10 +1962,10 @@
         <v>57</v>
       </c>
       <c r="E24" s="13">
-        <v>3500</v>
+        <v>3100</v>
       </c>
       <c r="F24" s="13">
-        <v>5000</v>
+        <v>4100</v>
       </c>
       <c r="G24" s="16">
         <v>2</v>
@@ -1986,10 +1986,10 @@
         <v>59</v>
       </c>
       <c r="E25" s="13">
-        <v>3500</v>
+        <v>3100</v>
       </c>
       <c r="F25" s="13">
-        <v>5000</v>
+        <v>4100</v>
       </c>
       <c r="G25" s="16">
         <v>3</v>
@@ -2010,10 +2010,10 @@
         <v>61</v>
       </c>
       <c r="E26" s="13">
-        <v>3000</v>
+        <v>2400</v>
       </c>
       <c r="F26" s="13">
-        <v>4200</v>
+        <v>3800</v>
       </c>
       <c r="G26" s="16">
         <v>4</v>
@@ -2034,10 +2034,10 @@
         <v>63</v>
       </c>
       <c r="E27" s="13">
-        <v>3000</v>
+        <v>2400</v>
       </c>
       <c r="F27" s="13">
-        <v>4200</v>
+        <v>3800</v>
       </c>
       <c r="G27" s="16">
         <v>5</v>
@@ -2058,10 +2058,10 @@
         <v>65</v>
       </c>
       <c r="E28" s="13">
-        <v>3000</v>
+        <v>2400</v>
       </c>
       <c r="F28" s="13">
-        <v>4200</v>
+        <v>3800</v>
       </c>
       <c r="G28" s="16">
         <v>6</v>
@@ -2082,10 +2082,10 @@
         <v>67</v>
       </c>
       <c r="E29" s="13">
-        <v>3000</v>
+        <v>2400</v>
       </c>
       <c r="F29" s="13">
-        <v>4200</v>
+        <v>3800</v>
       </c>
       <c r="G29" s="16">
         <v>7</v>
@@ -2106,10 +2106,10 @@
         <v>69</v>
       </c>
       <c r="E30" s="13">
-        <v>3000</v>
+        <v>2400</v>
       </c>
       <c r="F30" s="13">
-        <v>4200</v>
+        <v>3800</v>
       </c>
       <c r="G30" s="16">
         <v>8</v>
@@ -2130,10 +2130,10 @@
         <v>71</v>
       </c>
       <c r="E31" s="13">
-        <v>3500</v>
+        <v>3100</v>
       </c>
       <c r="F31" s="13">
-        <v>5000</v>
+        <v>4100</v>
       </c>
       <c r="G31" s="16">
         <v>9</v>
@@ -2154,10 +2154,10 @@
         <v>73</v>
       </c>
       <c r="E32" s="13">
-        <v>3500</v>
+        <v>2700</v>
       </c>
       <c r="F32" s="13">
-        <v>5000</v>
+        <v>4200</v>
       </c>
       <c r="G32" s="16">
         <v>10</v>
@@ -2178,10 +2178,10 @@
         <v>75</v>
       </c>
       <c r="E33" s="13">
-        <v>3500</v>
+        <v>3100</v>
       </c>
       <c r="F33" s="13">
-        <v>5000</v>
+        <v>4100</v>
       </c>
       <c r="G33" s="16">
         <v>11</v>
@@ -2202,10 +2202,10 @@
         <v>77</v>
       </c>
       <c r="E34" s="13">
-        <v>3500</v>
+        <v>3100</v>
       </c>
       <c r="F34" s="13">
-        <v>5000</v>
+        <v>4100</v>
       </c>
       <c r="G34" s="16">
         <v>12</v>
@@ -2226,10 +2226,10 @@
         <v>79</v>
       </c>
       <c r="E35" s="13">
-        <v>3500</v>
+        <v>3100</v>
       </c>
       <c r="F35" s="13">
-        <v>5000</v>
+        <v>4100</v>
       </c>
       <c r="G35" s="16">
         <v>13</v>
@@ -2250,10 +2250,10 @@
         <v>81</v>
       </c>
       <c r="E36" s="13">
-        <v>3300</v>
+        <v>2700</v>
       </c>
       <c r="F36" s="13">
-        <v>4700</v>
+        <v>4200</v>
       </c>
       <c r="G36" s="16">
         <v>14</v>
@@ -2298,10 +2298,10 @@
         <v>86</v>
       </c>
       <c r="E38" s="13">
-        <v>1550</v>
+        <v>1750</v>
       </c>
       <c r="F38" s="13">
-        <v>2150</v>
+        <v>2300</v>
       </c>
       <c r="G38" s="16">
         <v>2</v>
@@ -2322,10 +2322,10 @@
         <v>88</v>
       </c>
       <c r="E39" s="13">
-        <v>2450</v>
+        <v>2700</v>
       </c>
       <c r="F39" s="13">
-        <v>3400</v>
+        <v>4700</v>
       </c>
       <c r="G39" s="16">
         <v>3</v>
@@ -2346,10 +2346,10 @@
         <v>90</v>
       </c>
       <c r="E40" s="13">
-        <v>600</v>
+        <v>1150</v>
       </c>
       <c r="F40" s="13">
-        <v>1050</v>
+        <v>1850</v>
       </c>
       <c r="G40" s="16">
         <v>4</v>
@@ -2370,10 +2370,10 @@
         <v>92</v>
       </c>
       <c r="E41" s="13">
-        <v>530</v>
+        <v>1150</v>
       </c>
       <c r="F41" s="13">
-        <v>1000</v>
+        <v>1850</v>
       </c>
       <c r="G41" s="16">
         <v>5</v>
@@ -2394,10 +2394,10 @@
         <v>94</v>
       </c>
       <c r="E42" s="13">
-        <v>650</v>
+        <v>1400</v>
       </c>
       <c r="F42" s="13">
-        <v>1200</v>
+        <v>2400</v>
       </c>
       <c r="G42" s="16">
         <v>6</v>
@@ -2418,10 +2418,10 @@
         <v>96</v>
       </c>
       <c r="E43" s="13">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="F43" s="13">
-        <v>1100</v>
+        <v>1250</v>
       </c>
       <c r="G43" s="16">
         <v>7</v>
@@ -2442,10 +2442,10 @@
         <v>98</v>
       </c>
       <c r="E44" s="13">
-        <v>550</v>
+        <v>1400</v>
       </c>
       <c r="F44" s="13">
-        <v>1000</v>
+        <v>2050</v>
       </c>
       <c r="G44" s="16">
         <v>8</v>
@@ -2466,10 +2466,10 @@
         <v>100</v>
       </c>
       <c r="E45" s="13">
-        <v>600</v>
+        <v>1570</v>
       </c>
       <c r="F45" s="13">
-        <v>1000</v>
+        <v>2540</v>
       </c>
       <c r="G45" s="16">
         <v>9</v>
@@ -2490,10 +2490,10 @@
         <v>102</v>
       </c>
       <c r="E46" s="13">
-        <v>470</v>
+        <v>700</v>
       </c>
       <c r="F46" s="13">
-        <v>850</v>
+        <v>1300</v>
       </c>
       <c r="G46" s="16">
         <v>10</v>
@@ -2514,10 +2514,10 @@
         <v>104</v>
       </c>
       <c r="E47" s="13">
-        <v>565</v>
+        <v>700</v>
       </c>
       <c r="F47" s="13">
-        <v>1080</v>
+        <v>1150</v>
       </c>
       <c r="G47" s="16">
         <v>11</v>
@@ -2538,10 +2538,10 @@
         <v>106</v>
       </c>
       <c r="E48" s="13">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="F48" s="13">
-        <v>400</v>
+        <v>650</v>
       </c>
       <c r="G48" s="16">
         <v>12</v>
@@ -2562,10 +2562,10 @@
         <v>108</v>
       </c>
       <c r="E49" s="13">
-        <v>420</v>
+        <v>650</v>
       </c>
       <c r="F49" s="13">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="G49" s="16">
         <v>13</v>
@@ -2586,10 +2586,10 @@
         <v>110</v>
       </c>
       <c r="E50" s="13">
-        <v>600</v>
+        <v>1570</v>
       </c>
       <c r="F50" s="13">
-        <v>1100</v>
+        <v>2540</v>
       </c>
       <c r="G50" s="16">
         <v>14</v>
@@ -2610,10 +2610,10 @@
         <v>112</v>
       </c>
       <c r="E51" s="13">
-        <v>185</v>
+        <v>400</v>
       </c>
       <c r="F51" s="13">
-        <v>360</v>
+        <v>600</v>
       </c>
       <c r="G51" s="16">
         <v>15</v>
@@ -2634,10 +2634,10 @@
         <v>114</v>
       </c>
       <c r="E52" s="13">
-        <v>310</v>
+        <v>450</v>
       </c>
       <c r="F52" s="13">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="G52" s="16">
         <v>16</v>
@@ -2658,10 +2658,10 @@
         <v>116</v>
       </c>
       <c r="E53" s="13">
-        <v>400</v>
+        <v>850</v>
       </c>
       <c r="F53" s="13">
-        <v>650</v>
+        <v>1300</v>
       </c>
       <c r="G53" s="16">
         <v>17</v>
@@ -2682,10 +2682,10 @@
         <v>118</v>
       </c>
       <c r="E54" s="13">
-        <v>200</v>
+        <v>450</v>
       </c>
       <c r="F54" s="13">
-        <v>350</v>
+        <v>850</v>
       </c>
       <c r="G54" s="16">
         <v>18</v>
@@ -2706,10 +2706,10 @@
         <v>120</v>
       </c>
       <c r="E55" s="13">
-        <v>2000</v>
+        <v>2780</v>
       </c>
       <c r="F55" s="13">
-        <v>2400</v>
+        <v>3560</v>
       </c>
       <c r="G55" s="16">
         <v>19</v>
@@ -2730,10 +2730,10 @@
         <v>122</v>
       </c>
       <c r="E56" s="13">
-        <v>1480</v>
+        <v>1600</v>
       </c>
       <c r="F56" s="13">
-        <v>2350</v>
+        <v>2400</v>
       </c>
       <c r="G56" s="16">
         <v>20</v>
@@ -2754,10 +2754,10 @@
         <v>124</v>
       </c>
       <c r="E57" s="13">
-        <v>2000</v>
+        <v>3080</v>
       </c>
       <c r="F57" s="13">
-        <v>2500</v>
+        <v>3960</v>
       </c>
       <c r="G57" s="16">
         <v>21</v>
@@ -2778,10 +2778,10 @@
         <v>126</v>
       </c>
       <c r="E58" s="13">
-        <v>2300</v>
+        <v>2950</v>
       </c>
       <c r="F58" s="13">
-        <v>3100</v>
+        <v>3900</v>
       </c>
       <c r="G58" s="16">
         <v>22</v>
@@ -2874,10 +2874,10 @@
         <v>135</v>
       </c>
       <c r="E62" s="13">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F62" s="13">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="G62" s="16">
         <v>4</v>
@@ -2898,10 +2898,10 @@
         <v>137</v>
       </c>
       <c r="E63" s="13">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F63" s="13">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="G63" s="16">
         <v>5</v>
@@ -2922,10 +2922,10 @@
         <v>139</v>
       </c>
       <c r="E64" s="13">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F64" s="13">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="G64" s="16">
         <v>6</v>
@@ -2946,10 +2946,10 @@
         <v>141</v>
       </c>
       <c r="E65" s="13">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F65" s="13">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="G65" s="16">
         <v>7</v>
@@ -2970,10 +2970,10 @@
         <v>143</v>
       </c>
       <c r="E66" s="13">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F66" s="13">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="G66" s="16">
         <v>8</v>
@@ -3114,10 +3114,10 @@
         <v>156</v>
       </c>
       <c r="E72" s="13">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="F72" s="13">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="G72" s="16">
         <v>6</v>
@@ -3138,10 +3138,10 @@
         <v>158</v>
       </c>
       <c r="E73" s="13">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F73" s="13">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="G73" s="16">
         <v>7</v>
@@ -3186,10 +3186,10 @@
         <v>162</v>
       </c>
       <c r="E75" s="13">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F75" s="13">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="G75" s="16">
         <v>9</v>
@@ -3210,10 +3210,10 @@
         <v>164</v>
       </c>
       <c r="E76" s="13">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F76" s="13">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="G76" s="16">
         <v>10</v>
@@ -3306,7 +3306,7 @@
         <v>173</v>
       </c>
       <c r="E80" s="13">
-        <v>3250</v>
+        <v>3400</v>
       </c>
       <c r="F80" s="13">
         <v>4300</v>
@@ -3330,10 +3330,10 @@
         <v>175</v>
       </c>
       <c r="E81" s="13">
-        <v>3600</v>
+        <v>4000</v>
       </c>
       <c r="F81" s="13">
-        <v>4250</v>
+        <v>4000</v>
       </c>
       <c r="G81" s="16">
         <v>2</v>
@@ -3354,10 +3354,10 @@
         <v>177</v>
       </c>
       <c r="E82" s="13">
-        <v>3250</v>
+        <v>3400</v>
       </c>
       <c r="F82" s="13">
-        <v>4400</v>
+        <v>3700</v>
       </c>
       <c r="G82" s="16">
         <v>3</v>
@@ -3378,10 +3378,10 @@
         <v>179</v>
       </c>
       <c r="E83" s="13">
-        <v>3400</v>
+        <v>3750</v>
       </c>
       <c r="F83" s="13">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="G83" s="16">
         <v>4</v>
@@ -3405,7 +3405,7 @@
         <v>4300</v>
       </c>
       <c r="F84" s="13">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="G84" s="16">
         <v>5</v>
@@ -3426,10 +3426,10 @@
         <v>183</v>
       </c>
       <c r="E85" s="13">
-        <v>3650</v>
+        <v>3000</v>
       </c>
       <c r="F85" s="13">
-        <v>5300</v>
+        <v>3900</v>
       </c>
       <c r="G85" s="16">
         <v>6</v>
@@ -3450,10 +3450,10 @@
         <v>185</v>
       </c>
       <c r="E86" s="13">
-        <v>7100</v>
+        <v>3300</v>
       </c>
       <c r="F86" s="13">
-        <v>8500</v>
+        <v>5100</v>
       </c>
       <c r="G86" s="16">
         <v>7</v>
@@ -3474,10 +3474,10 @@
         <v>187</v>
       </c>
       <c r="E87" s="13">
-        <v>4800</v>
+        <v>3400</v>
       </c>
       <c r="F87" s="13">
-        <v>5800</v>
+        <v>4600</v>
       </c>
       <c r="G87" s="16">
         <v>8</v>
@@ -3546,10 +3546,10 @@
         <v>193</v>
       </c>
       <c r="E90" s="13">
-        <v>2900</v>
+        <v>3560</v>
       </c>
       <c r="F90" s="13">
-        <v>3500</v>
+        <v>4450</v>
       </c>
       <c r="G90" s="16">
         <v>11</v>
@@ -3570,10 +3570,10 @@
         <v>195</v>
       </c>
       <c r="E91" s="13">
-        <v>2500</v>
+        <v>3410</v>
       </c>
       <c r="F91" s="13">
-        <v>3300</v>
+        <v>4320</v>
       </c>
       <c r="G91" s="16">
         <v>12</v>
@@ -3594,10 +3594,10 @@
         <v>198</v>
       </c>
       <c r="E92" s="13">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="F92" s="13">
-        <v>4950</v>
+        <v>4960</v>
       </c>
       <c r="G92" s="16">
         <v>1</v>
@@ -3618,10 +3618,10 @@
         <v>199</v>
       </c>
       <c r="E93" s="13">
-        <v>2650</v>
+        <v>2550</v>
       </c>
       <c r="F93" s="13">
-        <v>5200</v>
+        <v>5000</v>
       </c>
       <c r="G93" s="16">
         <v>2</v>
@@ -3642,10 +3642,10 @@
         <v>201</v>
       </c>
       <c r="E94" s="13">
-        <v>2600</v>
+        <v>2550</v>
       </c>
       <c r="F94" s="13">
-        <v>5150</v>
+        <v>4950</v>
       </c>
       <c r="G94" s="16">
         <v>3</v>
@@ -3666,10 +3666,10 @@
         <v>203</v>
       </c>
       <c r="E95" s="13">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="F95" s="13">
-        <v>4950</v>
+        <v>4960</v>
       </c>
       <c r="G95" s="16">
         <v>4</v>
@@ -3690,10 +3690,10 @@
         <v>205</v>
       </c>
       <c r="E96" s="13">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="F96" s="13">
-        <v>4950</v>
+        <v>4960</v>
       </c>
       <c r="G96" s="16">
         <v>5</v>
@@ -3714,10 +3714,10 @@
         <v>208</v>
       </c>
       <c r="E97" s="13">
-        <v>8000</v>
+        <v>8700</v>
       </c>
       <c r="F97" s="13">
-        <v>13000</v>
+        <v>12800</v>
       </c>
       <c r="G97" s="16">
         <v>1</v>
@@ -3738,10 +3738,10 @@
         <v>210</v>
       </c>
       <c r="E98" s="13">
-        <v>7000</v>
+        <v>8700</v>
       </c>
       <c r="F98" s="13">
-        <v>11000</v>
+        <v>12800</v>
       </c>
       <c r="G98" s="16">
         <v>2</v>
@@ -3762,10 +3762,10 @@
         <v>212</v>
       </c>
       <c r="E99" s="13">
-        <v>5450</v>
+        <v>6500</v>
       </c>
       <c r="F99" s="13">
-        <v>7000</v>
+        <v>8200</v>
       </c>
       <c r="G99" s="16">
         <v>3</v>
@@ -3786,10 +3786,10 @@
         <v>214</v>
       </c>
       <c r="E100" s="13">
-        <v>7250</v>
+        <v>9100</v>
       </c>
       <c r="F100" s="13">
-        <v>8800</v>
+        <v>13600</v>
       </c>
       <c r="G100" s="16">
         <v>4</v>
@@ -3810,10 +3810,10 @@
         <v>216</v>
       </c>
       <c r="E101" s="13">
-        <v>5100</v>
+        <v>6400</v>
       </c>
       <c r="F101" s="13">
-        <v>6600</v>
+        <v>8000</v>
       </c>
       <c r="G101" s="16">
         <v>5</v>
@@ -3834,7 +3834,7 @@
         <v>219</v>
       </c>
       <c r="E102" s="13">
-        <v>4900</v>
+        <v>4700</v>
       </c>
       <c r="F102" s="13">
         <v>7600</v>
@@ -3858,7 +3858,7 @@
         <v>221</v>
       </c>
       <c r="E103" s="13">
-        <v>4800</v>
+        <v>4600</v>
       </c>
       <c r="F103" s="13">
         <v>7600</v>
@@ -3906,10 +3906,10 @@
         <v>225</v>
       </c>
       <c r="E105" s="13">
-        <v>3400</v>
+        <v>3500</v>
       </c>
       <c r="F105" s="13">
-        <v>5200</v>
+        <v>5300</v>
       </c>
       <c r="G105" s="16">
         <v>4</v>
@@ -3930,10 +3930,10 @@
         <v>227</v>
       </c>
       <c r="E106" s="13">
-        <v>5350</v>
+        <v>5250</v>
       </c>
       <c r="F106" s="13">
-        <v>6950</v>
+        <v>7150</v>
       </c>
       <c r="G106" s="16">
         <v>5</v>
@@ -3954,10 +3954,10 @@
         <v>229</v>
       </c>
       <c r="E107" s="14">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="F107" s="14">
-        <v>3500</v>
+        <v>3400</v>
       </c>
       <c r="G107" s="17">
         <v>6</v>
